--- a/Design-Files/WIFI_Board_RGB-LCDV4.0/BOM/BOM With Price WIFI_Board_RGB-LCDV4.0.xlsx
+++ b/Design-Files/WIFI_Board_RGB-LCDV4.0/BOM/BOM With Price WIFI_Board_RGB-LCDV4.0.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7620" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="5 Boards" sheetId="1" r:id="rId1"/>
-    <sheet name="100 Boards" sheetId="2" r:id="rId2"/>
+    <sheet name="10 Boards" sheetId="3" r:id="rId2"/>
+    <sheet name="100 Boards" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2098" uniqueCount="441">
   <si>
     <t>#</t>
   </si>
@@ -1321,6 +1322,21 @@
   </si>
   <si>
     <t>Single Board Cost</t>
+  </si>
+  <si>
+    <t>Quantity (10 Boards)</t>
+  </si>
+  <si>
+    <t>MOQ (10 Boards)</t>
+  </si>
+  <si>
+    <t>Unit Cost (10 Boards)</t>
+  </si>
+  <si>
+    <t>Total Cost (10 Boards)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Remarks</t>
   </si>
   <si>
     <t>Quantity (100 Boards)</t>
@@ -1812,7 +1828,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -1926,6 +1942,19 @@
         <color auto="1"/>
       </right>
       <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
@@ -2053,7 +2082,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2065,34 +2094,34 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2177,7 +2206,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2273,14 +2302,20 @@
     <xf numFmtId="179" fontId="15" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2610,8 +2645,8 @@
   <dimension ref="A1:R69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="3.14285714285714" style="33" customWidth="1"/>
-    <col min="3" max="3" width="18" style="33" customWidth="1"/>
+    <col min="2" max="2" width="3.14285714285714" style="37" customWidth="1"/>
+    <col min="3" max="3" width="18" style="37" customWidth="1"/>
     <col min="4" max="4" width="27.4285714285714" customWidth="1"/>
     <col min="5" max="5" width="30.8571428571429" customWidth="1"/>
     <col min="6" max="6" width="18.7142857142857" customWidth="1"/>
@@ -2752,7 +2787,7 @@
         <v>0.0012</v>
       </c>
       <c r="Q3" s="17">
-        <f t="shared" ref="Q3:Q66" si="2">P3*N3</f>
+        <f t="shared" ref="Q3:Q67" si="2">P3*N3</f>
         <v>0.12</v>
       </c>
       <c r="R3" s="9"/>
@@ -2904,7 +2939,7 @@
       <c r="N6" s="12">
         <v>10</v>
       </c>
-      <c r="O6" s="34" t="s">
+      <c r="O6" s="35" t="s">
         <v>25</v>
       </c>
       <c r="P6" s="19">
@@ -3010,7 +3045,7 @@
       <c r="N8" s="12">
         <v>5</v>
       </c>
-      <c r="O8" s="34" t="s">
+      <c r="O8" s="35" t="s">
         <v>63</v>
       </c>
       <c r="P8" s="19">
@@ -3964,7 +3999,7 @@
       <c r="N26" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="O26" s="35" t="s">
+      <c r="O26" s="36" t="s">
         <v>25</v>
       </c>
       <c r="P26" s="19">
@@ -4070,7 +4105,7 @@
       <c r="N28" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="O28" s="35" t="s">
+      <c r="O28" s="36" t="s">
         <v>63</v>
       </c>
       <c r="P28" s="19">
@@ -4123,7 +4158,7 @@
       <c r="N29" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="O29" s="35" t="s">
+      <c r="O29" s="36" t="s">
         <v>25</v>
       </c>
       <c r="P29" s="17" t="s">
@@ -4176,7 +4211,7 @@
       <c r="N30" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="O30" s="35" t="s">
+      <c r="O30" s="36" t="s">
         <v>25</v>
       </c>
       <c r="P30" s="19" t="s">
@@ -6150,7 +6185,7 @@
         <v>15.26</v>
       </c>
       <c r="Q67" s="19">
-        <f>P67*N67</f>
+        <f t="shared" si="2"/>
         <v>76.3</v>
       </c>
       <c r="R67" s="12"/>
@@ -6268,6 +6303,3659 @@
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="3.57142857142857" customWidth="1"/>
+    <col min="3" max="3" width="14.7142857142857" customWidth="1"/>
+    <col min="4" max="4" width="17.1428571428571" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="7" max="7" width="27.2857142857143" customWidth="1"/>
+    <col min="8" max="8" width="14.1428571428571" customWidth="1"/>
+    <col min="9" max="9" width="23.1428571428571" customWidth="1"/>
+    <col min="10" max="10" width="18.2857142857143" customWidth="1"/>
+    <col min="11" max="11" width="8.85714285714286" customWidth="1"/>
+    <col min="12" max="12" width="9.28571428571429" customWidth="1"/>
+    <col min="13" max="13" width="19.5714285714286" customWidth="1"/>
+    <col min="14" max="14" width="16.7142857142857" customWidth="1"/>
+    <col min="16" max="16" width="20.1428571428571" customWidth="1"/>
+    <col min="17" max="17" width="20.7142857142857" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" spans="1:18">
+      <c r="A1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+    </row>
+    <row r="2" ht="15.75" spans="1:18">
+      <c r="A2" s="2"/>
+      <c r="B2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="N2" s="33" t="s">
+        <v>432</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="34" t="s">
+        <v>433</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3" s="2"/>
+      <c r="B3" s="7">
+        <f>ROW(B3)-ROW($B$2)</f>
+        <v>1</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="9">
+        <v>2</v>
+      </c>
+      <c r="M3" s="9">
+        <f>L3*10</f>
+        <v>20</v>
+      </c>
+      <c r="N3" s="9">
+        <v>100</v>
+      </c>
+      <c r="O3" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="P3" s="17">
+        <v>0.0012</v>
+      </c>
+      <c r="Q3" s="17">
+        <f t="shared" ref="Q3:Q30" si="0">P3*N3</f>
+        <v>0.12</v>
+      </c>
+      <c r="R3" s="9"/>
+    </row>
+    <row r="4" ht="36" spans="1:18">
+      <c r="A4" s="2"/>
+      <c r="B4" s="10">
+        <f>ROW(B4)-ROW($B$2)</f>
+        <v>2</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="12">
+        <v>1</v>
+      </c>
+      <c r="M4" s="9">
+        <f t="shared" ref="M4:M35" si="1">L4*10</f>
+        <v>10</v>
+      </c>
+      <c r="N4" s="12">
+        <v>10</v>
+      </c>
+      <c r="O4" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="P4" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q4" s="19">
+        <f t="shared" si="0"/>
+        <v>8.029</v>
+      </c>
+      <c r="R4" s="12"/>
+    </row>
+    <row r="5" ht="36" spans="1:18">
+      <c r="A5" s="2"/>
+      <c r="B5" s="7">
+        <f>ROW(B5)-ROW($B$2)</f>
+        <v>3</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5" s="9">
+        <v>4</v>
+      </c>
+      <c r="M5" s="9">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="O5" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="P5" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.19</v>
+      </c>
+      <c r="R5" s="9"/>
+    </row>
+    <row r="6" ht="36" spans="1:18">
+      <c r="A6" s="2"/>
+      <c r="B6" s="10">
+        <f>ROW(B6)-ROW($B$2)</f>
+        <v>4</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="L6" s="12">
+        <v>1</v>
+      </c>
+      <c r="M6" s="9">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N6" s="12">
+        <v>10</v>
+      </c>
+      <c r="O6" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="P6" s="19">
+        <v>0.0393</v>
+      </c>
+      <c r="Q6" s="19">
+        <f t="shared" si="0"/>
+        <v>0.393</v>
+      </c>
+      <c r="R6" s="12"/>
+    </row>
+    <row r="7" ht="36" spans="1:18">
+      <c r="A7" s="2"/>
+      <c r="B7" s="7">
+        <f>ROW(B7)-ROW($B$2)</f>
+        <v>5</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7" s="9">
+        <v>1</v>
+      </c>
+      <c r="M7" s="9">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="O7" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="P7" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.534</v>
+      </c>
+      <c r="R7" s="9"/>
+    </row>
+    <row r="8" ht="72" spans="1:18">
+      <c r="A8" s="2"/>
+      <c r="B8" s="10">
+        <f>ROW(B8)-ROW($B$2)</f>
+        <v>6</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="L8" s="12">
+        <v>1</v>
+      </c>
+      <c r="M8" s="9">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N8" s="12">
+        <v>10</v>
+      </c>
+      <c r="O8" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="P8" s="19">
+        <v>0.77</v>
+      </c>
+      <c r="Q8" s="19">
+        <f t="shared" si="0"/>
+        <v>7.7</v>
+      </c>
+      <c r="R8" s="12"/>
+    </row>
+    <row r="9" ht="36" spans="1:18">
+      <c r="A9" s="2"/>
+      <c r="B9" s="7">
+        <f>ROW(B9)-ROW($B$2)</f>
+        <v>7</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="L9" s="9">
+        <v>4</v>
+      </c>
+      <c r="M9" s="9">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="O9" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="P9" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.18</v>
+      </c>
+      <c r="R9" s="9"/>
+    </row>
+    <row r="10" ht="36" spans="1:18">
+      <c r="A10" s="2"/>
+      <c r="B10" s="10">
+        <f>ROW(B10)-ROW($B$2)</f>
+        <v>8</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="L10" s="12">
+        <v>1</v>
+      </c>
+      <c r="M10" s="9">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N10" s="12">
+        <v>10</v>
+      </c>
+      <c r="O10" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="P10" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q10" s="19">
+        <f t="shared" si="0"/>
+        <v>1.342</v>
+      </c>
+      <c r="R10" s="12"/>
+    </row>
+    <row r="11" ht="36" spans="1:18">
+      <c r="A11" s="2"/>
+      <c r="B11" s="7">
+        <f>ROW(B11)-ROW($B$2)</f>
+        <v>9</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="L11" s="9">
+        <v>3</v>
+      </c>
+      <c r="M11" s="9">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="O11" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="P11" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q11" s="17">
+        <f t="shared" si="0"/>
+        <v>0.34</v>
+      </c>
+      <c r="R11" s="9"/>
+    </row>
+    <row r="12" ht="36" spans="1:18">
+      <c r="A12" s="2"/>
+      <c r="B12" s="10">
+        <f>ROW(B12)-ROW($B$2)</f>
+        <v>10</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="L12" s="12">
+        <v>1</v>
+      </c>
+      <c r="M12" s="9">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N12" s="12">
+        <v>10</v>
+      </c>
+      <c r="O12" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="P12" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q12" s="19">
+        <f t="shared" si="0"/>
+        <v>0.985</v>
+      </c>
+      <c r="R12" s="12"/>
+    </row>
+    <row r="13" ht="36" spans="1:18">
+      <c r="A13" s="2"/>
+      <c r="B13" s="7">
+        <f>ROW(B13)-ROW($B$2)</f>
+        <v>11</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="L13" s="9">
+        <v>1</v>
+      </c>
+      <c r="M13" s="9">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="O13" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="P13" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q13" s="17">
+        <f t="shared" si="0"/>
+        <v>0.31</v>
+      </c>
+      <c r="R13" s="9"/>
+    </row>
+    <row r="14" ht="36" spans="1:18">
+      <c r="A14" s="2"/>
+      <c r="B14" s="10">
+        <f>ROW(B14)-ROW($B$2)</f>
+        <v>12</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="K14" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="L14" s="12">
+        <v>2</v>
+      </c>
+      <c r="M14" s="9">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N14" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="O14" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="P14" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q14" s="19">
+        <f t="shared" si="0"/>
+        <v>0.738</v>
+      </c>
+      <c r="R14" s="12"/>
+    </row>
+    <row r="15" ht="36" spans="1:18">
+      <c r="A15" s="2"/>
+      <c r="B15" s="7">
+        <f>ROW(B15)-ROW($B$2)</f>
+        <v>13</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="L15" s="9">
+        <v>1</v>
+      </c>
+      <c r="M15" s="9">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="O15" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="P15" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q15" s="17">
+        <f t="shared" si="0"/>
+        <v>0.235</v>
+      </c>
+      <c r="R15" s="9"/>
+    </row>
+    <row r="16" ht="108" spans="1:18">
+      <c r="A16" s="2"/>
+      <c r="B16" s="10">
+        <f>ROW(B16)-ROW($B$2)</f>
+        <v>14</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="K16" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="L16" s="12">
+        <v>1</v>
+      </c>
+      <c r="M16" s="9">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="O16" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="P16" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q16" s="19">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="R16" s="12"/>
+    </row>
+    <row r="17" ht="48" spans="1:18">
+      <c r="A17" s="2"/>
+      <c r="B17" s="7">
+        <f>ROW(B17)-ROW($B$2)</f>
+        <v>15</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="L17" s="9">
+        <v>2</v>
+      </c>
+      <c r="M17" s="9">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="O17" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="P17" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q17" s="17">
+        <f t="shared" si="0"/>
+        <v>0.43</v>
+      </c>
+      <c r="R17" s="9"/>
+    </row>
+    <row r="18" ht="120" spans="1:18">
+      <c r="A18" s="2"/>
+      <c r="B18" s="10">
+        <f>ROW(B18)-ROW($B$2)</f>
+        <v>16</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="K18" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="L18" s="12">
+        <v>1</v>
+      </c>
+      <c r="M18" s="9">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N18" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="O18" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="P18" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q18" s="19">
+        <f t="shared" si="0"/>
+        <v>0.41</v>
+      </c>
+      <c r="R18" s="12"/>
+    </row>
+    <row r="19" ht="48" spans="1:18">
+      <c r="A19" s="2"/>
+      <c r="B19" s="7">
+        <f>ROW(B19)-ROW($B$2)</f>
+        <v>17</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="K19" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="L19" s="9">
+        <v>1</v>
+      </c>
+      <c r="M19" s="9">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N19" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="O19" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="P19" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q19" s="17">
+        <f t="shared" si="0"/>
+        <v>0.61</v>
+      </c>
+      <c r="R19" s="9"/>
+    </row>
+    <row r="20" ht="48" spans="1:18">
+      <c r="A20" s="2"/>
+      <c r="B20" s="10">
+        <f>ROW(B20)-ROW($B$2)</f>
+        <v>18</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="K20" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="L20" s="12">
+        <v>1</v>
+      </c>
+      <c r="M20" s="9">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N20" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="O20" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="P20" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q20" s="19">
+        <f t="shared" si="0"/>
+        <v>0.805</v>
+      </c>
+      <c r="R20" s="12"/>
+    </row>
+    <row r="21" ht="96" spans="1:18">
+      <c r="A21" s="2"/>
+      <c r="B21" s="7">
+        <f>ROW(B21)-ROW($B$2)</f>
+        <v>19</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="K21" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="L21" s="9">
+        <v>6</v>
+      </c>
+      <c r="M21" s="9">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="N21" s="9">
+        <v>60</v>
+      </c>
+      <c r="O21" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="P21" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q21" s="17">
+        <f t="shared" si="0"/>
+        <v>0.528</v>
+      </c>
+      <c r="R21" s="9"/>
+    </row>
+    <row r="22" ht="48" spans="1:18">
+      <c r="A22" s="2"/>
+      <c r="B22" s="10">
+        <f>ROW(B22)-ROW($B$2)</f>
+        <v>20</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K22" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="L22" s="12">
+        <v>1</v>
+      </c>
+      <c r="M22" s="9">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N22" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="O22" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="P22" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q22" s="19">
+        <f t="shared" si="0"/>
+        <v>0.448</v>
+      </c>
+      <c r="R22" s="12"/>
+    </row>
+    <row r="23" ht="48" spans="1:18">
+      <c r="A23" s="2"/>
+      <c r="B23" s="7">
+        <f>ROW(B23)-ROW($B$2)</f>
+        <v>21</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="K23" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="L23" s="9">
+        <v>1</v>
+      </c>
+      <c r="M23" s="9">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N23" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="O23" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="P23" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q23" s="17">
+        <f t="shared" si="0"/>
+        <v>0.636</v>
+      </c>
+      <c r="R23" s="9"/>
+    </row>
+    <row r="24" ht="108" spans="1:18">
+      <c r="A24" s="2"/>
+      <c r="B24" s="10">
+        <f>ROW(B24)-ROW($B$2)</f>
+        <v>22</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="K24" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="L24" s="12">
+        <v>1</v>
+      </c>
+      <c r="M24" s="9">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N24" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="O24" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="P24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q24" s="19">
+        <f t="shared" si="0"/>
+        <v>0.8628</v>
+      </c>
+      <c r="R24" s="12"/>
+    </row>
+    <row r="25" ht="72" spans="1:18">
+      <c r="A25" s="2"/>
+      <c r="B25" s="7">
+        <f>ROW(B25)-ROW($B$2)</f>
+        <v>23</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="K25" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="L25" s="9">
+        <v>1</v>
+      </c>
+      <c r="M25" s="9">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N25" s="9">
+        <v>10</v>
+      </c>
+      <c r="O25" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="P25" s="17">
+        <v>0.174</v>
+      </c>
+      <c r="Q25" s="17">
+        <f t="shared" si="0"/>
+        <v>1.74</v>
+      </c>
+      <c r="R25" s="9"/>
+    </row>
+    <row r="26" ht="240" spans="1:18">
+      <c r="A26" s="2"/>
+      <c r="B26" s="10">
+        <f>ROW(B26)-ROW($B$2)</f>
+        <v>24</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="H26" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="K26" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="L26" s="12">
+        <v>1</v>
+      </c>
+      <c r="M26" s="9">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N26" s="12">
+        <v>10</v>
+      </c>
+      <c r="O26" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="P26" s="19">
+        <v>0.1187</v>
+      </c>
+      <c r="Q26" s="19">
+        <f t="shared" si="0"/>
+        <v>1.187</v>
+      </c>
+      <c r="R26" s="12"/>
+    </row>
+    <row r="27" ht="72" spans="1:18">
+      <c r="A27" s="2"/>
+      <c r="B27" s="7">
+        <f>ROW(B27)-ROW($B$2)</f>
+        <v>25</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="K27" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="L27" s="9">
+        <v>1</v>
+      </c>
+      <c r="M27" s="9">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N27" s="9">
+        <v>10</v>
+      </c>
+      <c r="O27" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="P27" s="17">
+        <v>0.1706</v>
+      </c>
+      <c r="Q27" s="17">
+        <f t="shared" si="0"/>
+        <v>1.706</v>
+      </c>
+      <c r="R27" s="9"/>
+    </row>
+    <row r="28" ht="24" spans="1:18">
+      <c r="A28" s="2"/>
+      <c r="B28" s="10">
+        <f>ROW(B28)-ROW($B$2)</f>
+        <v>26</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="K28" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="L28" s="12">
+        <v>1</v>
+      </c>
+      <c r="M28" s="9">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N28" s="9">
+        <v>10</v>
+      </c>
+      <c r="O28" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="P28" s="19">
+        <v>0.69</v>
+      </c>
+      <c r="Q28" s="19">
+        <f t="shared" si="0"/>
+        <v>6.9</v>
+      </c>
+      <c r="R28" s="12"/>
+    </row>
+    <row r="29" ht="36" spans="1:18">
+      <c r="A29" s="2"/>
+      <c r="B29" s="7">
+        <f>ROW(B29)-ROW($B$2)</f>
+        <v>27</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="L29" s="9">
+        <v>1</v>
+      </c>
+      <c r="M29" s="9">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N29" s="9">
+        <v>10</v>
+      </c>
+      <c r="O29" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="P29" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q29" s="17">
+        <f t="shared" si="0"/>
+        <v>0.978</v>
+      </c>
+      <c r="R29" s="9"/>
+    </row>
+    <row r="30" ht="36" spans="1:18">
+      <c r="A30" s="2"/>
+      <c r="B30" s="10">
+        <f>ROW(B30)-ROW($B$2)</f>
+        <v>28</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="L30" s="12">
+        <v>1</v>
+      </c>
+      <c r="M30" s="9">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N30" s="9">
+        <v>10</v>
+      </c>
+      <c r="O30" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="P30" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q30" s="19">
+        <f t="shared" si="0"/>
+        <v>3.35</v>
+      </c>
+      <c r="R30" s="12"/>
+    </row>
+    <row r="31" ht="24" spans="1:18">
+      <c r="A31" s="2"/>
+      <c r="B31" s="7">
+        <f>ROW(B31)-ROW($B$2)</f>
+        <v>29</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="I31" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="J31" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="L31" s="13">
+        <v>5</v>
+      </c>
+      <c r="M31" s="9">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N31" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="O31" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="P31" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q31" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="R31" s="27" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="32" ht="108" spans="1:18">
+      <c r="A32" s="2"/>
+      <c r="B32" s="10">
+        <f>ROW(B32)-ROW($B$2)</f>
+        <v>30</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="G32" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="H32" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="K32" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="L32" s="12">
+        <v>2</v>
+      </c>
+      <c r="M32" s="9">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N32" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="O32" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="P32" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q32" s="19">
+        <f t="shared" ref="Q32:Q40" si="2">P32*N32</f>
+        <v>0.75</v>
+      </c>
+      <c r="R32" s="12"/>
+    </row>
+    <row r="33" ht="120" spans="1:18">
+      <c r="A33" s="2"/>
+      <c r="B33" s="7">
+        <f>ROW(B33)-ROW($B$2)</f>
+        <v>31</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="L33" s="9">
+        <v>1</v>
+      </c>
+      <c r="M33" s="9">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N33" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="O33" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="P33" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q33" s="17">
+        <f t="shared" si="2"/>
+        <v>0.518</v>
+      </c>
+      <c r="R33" s="9"/>
+    </row>
+    <row r="34" ht="36" spans="1:18">
+      <c r="A34" s="2"/>
+      <c r="B34" s="10">
+        <f>ROW(B34)-ROW($B$2)</f>
+        <v>32</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="H34" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="L34" s="12">
+        <v>1</v>
+      </c>
+      <c r="M34" s="9">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N34" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="O34" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="P34" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q34" s="19">
+        <f t="shared" si="2"/>
+        <v>0.48</v>
+      </c>
+      <c r="R34" s="12"/>
+    </row>
+    <row r="35" ht="48" spans="1:18">
+      <c r="A35" s="2"/>
+      <c r="B35" s="7">
+        <f>ROW(B35)-ROW($B$2)</f>
+        <v>33</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="L35" s="9">
+        <v>4</v>
+      </c>
+      <c r="M35" s="9">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="N35" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="O35" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="P35" s="17" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q35" s="17">
+        <f t="shared" si="2"/>
+        <v>0.06</v>
+      </c>
+      <c r="R35" s="9"/>
+    </row>
+    <row r="36" ht="48" spans="1:18">
+      <c r="A36" s="2"/>
+      <c r="B36" s="10">
+        <f>ROW(B36)-ROW($B$2)</f>
+        <v>34</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="K36" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="L36" s="12">
+        <v>2</v>
+      </c>
+      <c r="M36" s="9">
+        <f t="shared" ref="M36:M67" si="3">L36*10</f>
+        <v>20</v>
+      </c>
+      <c r="N36" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="O36" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="P36" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q36" s="19">
+        <f t="shared" si="2"/>
+        <v>0.56</v>
+      </c>
+      <c r="R36" s="12"/>
+    </row>
+    <row r="37" ht="60" spans="1:18">
+      <c r="A37" s="2"/>
+      <c r="B37" s="7">
+        <f>ROW(B37)-ROW($B$2)</f>
+        <v>35</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="K37" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="L37" s="9">
+        <v>10</v>
+      </c>
+      <c r="M37" s="9">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="N37" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="O37" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="P37" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q37" s="17">
+        <f t="shared" si="2"/>
+        <v>0.11</v>
+      </c>
+      <c r="R37" s="9"/>
+    </row>
+    <row r="38" ht="48" spans="1:18">
+      <c r="A38" s="2"/>
+      <c r="B38" s="10">
+        <f>ROW(B38)-ROW($B$2)</f>
+        <v>36</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I38" s="12"/>
+      <c r="J38" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="K38" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="L38" s="12">
+        <v>3</v>
+      </c>
+      <c r="M38" s="9">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="N38" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="O38" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="P38" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q38" s="19">
+        <f t="shared" si="2"/>
+        <v>0.12</v>
+      </c>
+      <c r="R38" s="12"/>
+    </row>
+    <row r="39" ht="48" spans="1:18">
+      <c r="A39" s="2"/>
+      <c r="B39" s="7">
+        <f>ROW(B39)-ROW($B$2)</f>
+        <v>37</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="K39" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="L39" s="9">
+        <v>6</v>
+      </c>
+      <c r="M39" s="9">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="N39" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="O39" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="P39" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q39" s="17">
+        <f t="shared" si="2"/>
+        <v>0.11</v>
+      </c>
+      <c r="R39" s="9"/>
+    </row>
+    <row r="40" ht="132" spans="1:18">
+      <c r="A40" s="2"/>
+      <c r="B40" s="10">
+        <f>ROW(B40)-ROW($B$2)</f>
+        <v>38</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="G40" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="H40" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="I40" s="12"/>
+      <c r="J40" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="K40" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="L40" s="12">
+        <v>1</v>
+      </c>
+      <c r="M40" s="9">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="N40" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="O40" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="P40" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q40" s="19">
+        <f t="shared" si="2"/>
+        <v>0.21</v>
+      </c>
+      <c r="R40" s="12"/>
+    </row>
+    <row r="41" ht="48" spans="1:18">
+      <c r="A41" s="2"/>
+      <c r="B41" s="7">
+        <f>ROW(B41)-ROW($B$2)</f>
+        <v>39</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="F41" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="H41" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I41" s="13"/>
+      <c r="J41" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="K41" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="L41" s="13">
+        <v>2</v>
+      </c>
+      <c r="M41" s="9">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="N41" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="O41" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="P41" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q41" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="R41" s="27" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="42" ht="48" spans="1:18">
+      <c r="A42" s="2"/>
+      <c r="B42" s="10">
+        <f>ROW(B42)-ROW($B$2)</f>
+        <v>40</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="H42" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I42" s="12"/>
+      <c r="J42" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="K42" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="L42" s="12">
+        <v>1</v>
+      </c>
+      <c r="M42" s="9">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="N42" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="O42" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="P42" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q42" s="19">
+        <f t="shared" ref="Q42:Q54" si="4">P42*N42</f>
+        <v>0.07</v>
+      </c>
+      <c r="R42" s="12"/>
+    </row>
+    <row r="43" ht="48" spans="1:18">
+      <c r="A43" s="2"/>
+      <c r="B43" s="7">
+        <f>ROW(B43)-ROW($B$2)</f>
+        <v>41</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I43" s="9"/>
+      <c r="J43" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="K43" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="L43" s="9">
+        <v>1</v>
+      </c>
+      <c r="M43" s="9">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="N43" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="O43" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="P43" s="17" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q43" s="17">
+        <f t="shared" si="4"/>
+        <v>0.07</v>
+      </c>
+      <c r="R43" s="9"/>
+    </row>
+    <row r="44" ht="48" spans="1:18">
+      <c r="A44" s="2"/>
+      <c r="B44" s="10">
+        <f>ROW(B44)-ROW($B$2)</f>
+        <v>42</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="G44" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="H44" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I44" s="12"/>
+      <c r="J44" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="K44" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="L44" s="12">
+        <v>1</v>
+      </c>
+      <c r="M44" s="9">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="N44" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="O44" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="P44" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q44" s="19">
+        <f t="shared" si="4"/>
+        <v>0.06</v>
+      </c>
+      <c r="R44" s="12"/>
+    </row>
+    <row r="45" ht="48" spans="1:18">
+      <c r="A45" s="2"/>
+      <c r="B45" s="7">
+        <f>ROW(B45)-ROW($B$2)</f>
+        <v>43</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I45" s="9"/>
+      <c r="J45" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="K45" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="L45" s="9">
+        <v>2</v>
+      </c>
+      <c r="M45" s="9">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="N45" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="O45" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="P45" s="17" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q45" s="17">
+        <f t="shared" si="4"/>
+        <v>0.06</v>
+      </c>
+      <c r="R45" s="9"/>
+    </row>
+    <row r="46" ht="48" spans="1:18">
+      <c r="A46" s="2"/>
+      <c r="B46" s="10">
+        <f>ROW(B46)-ROW($B$2)</f>
+        <v>44</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="F46" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="G46" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="H46" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I46" s="12"/>
+      <c r="J46" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="K46" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="L46" s="12">
+        <v>2</v>
+      </c>
+      <c r="M46" s="9">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="N46" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="O46" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="P46" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q46" s="19">
+        <f t="shared" si="4"/>
+        <v>0.07</v>
+      </c>
+      <c r="R46" s="12"/>
+    </row>
+    <row r="47" ht="48" spans="1:18">
+      <c r="A47" s="2"/>
+      <c r="B47" s="7">
+        <f>ROW(B47)-ROW($B$2)</f>
+        <v>45</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I47" s="9"/>
+      <c r="J47" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="K47" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="L47" s="9">
+        <v>5</v>
+      </c>
+      <c r="M47" s="9">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="N47" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="O47" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="P47" s="17" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q47" s="17">
+        <f t="shared" si="4"/>
+        <v>0.07</v>
+      </c>
+      <c r="R47" s="9"/>
+    </row>
+    <row r="48" ht="48" spans="1:18">
+      <c r="A48" s="2"/>
+      <c r="B48" s="10">
+        <f>ROW(B48)-ROW($B$2)</f>
+        <v>46</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="F48" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="G48" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="H48" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I48" s="12"/>
+      <c r="J48" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="K48" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="L48" s="12">
+        <v>1</v>
+      </c>
+      <c r="M48" s="9">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="N48" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="O48" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="P48" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q48" s="19">
+        <f t="shared" si="4"/>
+        <v>0.12</v>
+      </c>
+      <c r="R48" s="12"/>
+    </row>
+    <row r="49" ht="48" spans="1:18">
+      <c r="A49" s="2"/>
+      <c r="B49" s="7">
+        <f>ROW(B49)-ROW($B$2)</f>
+        <v>47</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I49" s="9"/>
+      <c r="J49" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="K49" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="L49" s="9">
+        <v>1</v>
+      </c>
+      <c r="M49" s="9">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="N49" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="O49" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="P49" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q49" s="17">
+        <f t="shared" si="4"/>
+        <v>0.53</v>
+      </c>
+      <c r="R49" s="9"/>
+    </row>
+    <row r="50" ht="48" spans="1:18">
+      <c r="A50" s="2"/>
+      <c r="B50" s="10">
+        <f>ROW(B50)-ROW($B$2)</f>
+        <v>48</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="F50" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="G50" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="H50" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="I50" s="12"/>
+      <c r="J50" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="K50" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="L50" s="12">
+        <v>4</v>
+      </c>
+      <c r="M50" s="9">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="N50" s="12">
+        <v>40</v>
+      </c>
+      <c r="O50" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="P50" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q50" s="19">
+        <f t="shared" si="4"/>
+        <v>1.12</v>
+      </c>
+      <c r="R50" s="12"/>
+    </row>
+    <row r="51" ht="48" spans="1:18">
+      <c r="A51" s="2"/>
+      <c r="B51" s="7">
+        <f>ROW(B51)-ROW($B$2)</f>
+        <v>49</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="H51" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I51" s="9"/>
+      <c r="J51" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="K51" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="L51" s="9">
+        <v>2</v>
+      </c>
+      <c r="M51" s="9">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="N51" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="O51" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="P51" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q51" s="17">
+        <f t="shared" si="4"/>
+        <v>0.11</v>
+      </c>
+      <c r="R51" s="9"/>
+    </row>
+    <row r="52" ht="48" spans="1:18">
+      <c r="A52" s="2"/>
+      <c r="B52" s="10">
+        <f>ROW(B52)-ROW($B$2)</f>
+        <v>50</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="F52" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="G52" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="H52" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I52" s="12"/>
+      <c r="J52" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="K52" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="L52" s="12">
+        <v>1</v>
+      </c>
+      <c r="M52" s="9">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="N52" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="O52" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="P52" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q52" s="19">
+        <f t="shared" si="4"/>
+        <v>0.12</v>
+      </c>
+      <c r="R52" s="12"/>
+    </row>
+    <row r="53" ht="48" spans="1:18">
+      <c r="A53" s="2"/>
+      <c r="B53" s="7">
+        <f>ROW(B53)-ROW($B$2)</f>
+        <v>51</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I53" s="9"/>
+      <c r="J53" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="K53" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="L53" s="9">
+        <v>1</v>
+      </c>
+      <c r="M53" s="9">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="N53" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="O53" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="P53" s="17" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q53" s="17">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="R53" s="9"/>
+    </row>
+    <row r="54" ht="48" spans="1:18">
+      <c r="A54" s="2"/>
+      <c r="B54" s="10">
+        <f>ROW(B54)-ROW($B$2)</f>
+        <v>52</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="E54" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="F54" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="G54" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="H54" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I54" s="12"/>
+      <c r="J54" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="K54" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="L54" s="12">
+        <v>1</v>
+      </c>
+      <c r="M54" s="9">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="N54" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="O54" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="P54" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q54" s="19">
+        <f t="shared" si="4"/>
+        <v>0.06</v>
+      </c>
+      <c r="R54" s="12"/>
+    </row>
+    <row r="55" ht="48" spans="1:18">
+      <c r="A55" s="2"/>
+      <c r="B55" s="7">
+        <f>ROW(B55)-ROW($B$2)</f>
+        <v>53</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="D55" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="E55" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="F55" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="G55" s="13" t="s">
+        <v>333</v>
+      </c>
+      <c r="H55" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="K55" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="L55" s="13">
+        <v>1</v>
+      </c>
+      <c r="M55" s="9">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="N55" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="O55" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="P55" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q55" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="R55" s="27" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="56" ht="48" spans="1:18">
+      <c r="A56" s="2"/>
+      <c r="B56" s="10">
+        <f>ROW(B56)-ROW($B$2)</f>
+        <v>54</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="E56" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="F56" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="G56" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="H56" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="I56" s="12"/>
+      <c r="J56" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="K56" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="L56" s="12">
+        <v>2</v>
+      </c>
+      <c r="M56" s="9">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="N56" s="12">
+        <v>20</v>
+      </c>
+      <c r="O56" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="P56" s="19" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q56" s="19">
+        <f t="shared" ref="Q56:Q67" si="5">P56*N56</f>
+        <v>3.054</v>
+      </c>
+      <c r="R56" s="12"/>
+    </row>
+    <row r="57" ht="48" spans="1:18">
+      <c r="A57" s="2"/>
+      <c r="B57" s="7">
+        <f>ROW(B57)-ROW($B$2)</f>
+        <v>55</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="I57" s="9"/>
+      <c r="J57" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="K57" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="L57" s="9">
+        <v>1</v>
+      </c>
+      <c r="M57" s="9">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="N57" s="9">
+        <v>10</v>
+      </c>
+      <c r="O57" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="P57" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q57" s="17">
+        <f t="shared" si="5"/>
+        <v>16.431</v>
+      </c>
+      <c r="R57" s="9"/>
+    </row>
+    <row r="58" ht="48" spans="1:18">
+      <c r="A58" s="2"/>
+      <c r="B58" s="10">
+        <f>ROW(B58)-ROW($B$2)</f>
+        <v>56</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="E58" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="F58" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="G58" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="H58" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="I58" s="12"/>
+      <c r="J58" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="K58" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="L58" s="12">
+        <v>3</v>
+      </c>
+      <c r="M58" s="9">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="N58" s="12">
+        <v>30</v>
+      </c>
+      <c r="O58" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="P58" s="19" t="s">
+        <v>363</v>
+      </c>
+      <c r="Q58" s="19">
+        <f t="shared" si="5"/>
+        <v>20.859</v>
+      </c>
+      <c r="R58" s="12"/>
+    </row>
+    <row r="59" ht="24" spans="1:18">
+      <c r="A59" s="2"/>
+      <c r="B59" s="7">
+        <f>ROW(B59)-ROW($B$2)</f>
+        <v>57</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="H59" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="I59" s="9"/>
+      <c r="J59" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="K59" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="L59" s="9">
+        <v>1</v>
+      </c>
+      <c r="M59" s="9">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="N59" s="9">
+        <v>10</v>
+      </c>
+      <c r="O59" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="P59" s="17" t="s">
+        <v>371</v>
+      </c>
+      <c r="Q59" s="17">
+        <f t="shared" si="5"/>
+        <v>49.857</v>
+      </c>
+      <c r="R59" s="9"/>
+    </row>
+    <row r="60" ht="24" spans="1:18">
+      <c r="A60" s="2"/>
+      <c r="B60" s="10">
+        <f>ROW(B60)-ROW($B$2)</f>
+        <v>58</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="F60" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="G60" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="H60" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="I60" s="12"/>
+      <c r="J60" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="K60" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="L60" s="12">
+        <v>1</v>
+      </c>
+      <c r="M60" s="9">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="N60" s="9">
+        <v>10</v>
+      </c>
+      <c r="O60" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="P60" s="19" t="s">
+        <v>378</v>
+      </c>
+      <c r="Q60" s="19">
+        <f t="shared" si="5"/>
+        <v>9.333</v>
+      </c>
+      <c r="R60" s="12"/>
+    </row>
+    <row r="61" ht="24" spans="1:18">
+      <c r="A61" s="2"/>
+      <c r="B61" s="7">
+        <f>ROW(B61)-ROW($B$2)</f>
+        <v>59</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="I61" s="9"/>
+      <c r="J61" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="K61" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="L61" s="9">
+        <v>1</v>
+      </c>
+      <c r="M61" s="9">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="N61" s="9">
+        <v>10</v>
+      </c>
+      <c r="O61" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="P61" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="Q61" s="17">
+        <f t="shared" si="5"/>
+        <v>7.327</v>
+      </c>
+      <c r="R61" s="9"/>
+    </row>
+    <row r="62" ht="48" spans="1:18">
+      <c r="A62" s="2"/>
+      <c r="B62" s="10">
+        <f>ROW(B62)-ROW($B$2)</f>
+        <v>60</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="F62" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="G62" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="H62" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="I62" s="12"/>
+      <c r="J62" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="K62" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="L62" s="12">
+        <v>1</v>
+      </c>
+      <c r="M62" s="9">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="N62" s="12">
+        <v>10</v>
+      </c>
+      <c r="O62" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="P62" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q62" s="19">
+        <f t="shared" si="5"/>
+        <v>0.383</v>
+      </c>
+      <c r="R62" s="12"/>
+    </row>
+    <row r="63" ht="24" spans="1:18">
+      <c r="A63" s="2"/>
+      <c r="B63" s="7">
+        <f>ROW(B63)-ROW($B$2)</f>
+        <v>61</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="I63" s="9"/>
+      <c r="J63" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="K63" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="L63" s="9">
+        <v>1</v>
+      </c>
+      <c r="M63" s="9">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="N63" s="9">
+        <v>10</v>
+      </c>
+      <c r="O63" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="P63" s="17" t="s">
+        <v>401</v>
+      </c>
+      <c r="Q63" s="17">
+        <f t="shared" si="5"/>
+        <v>1.879</v>
+      </c>
+      <c r="R63" s="9"/>
+    </row>
+    <row r="64" ht="24" spans="1:18">
+      <c r="A64" s="2"/>
+      <c r="B64" s="10">
+        <f>ROW(B64)-ROW($B$2)</f>
+        <v>62</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="E64" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="F64" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="G64" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="H64" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="I64" s="12"/>
+      <c r="J64" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="K64" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="L64" s="12">
+        <v>1</v>
+      </c>
+      <c r="M64" s="9">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="N64" s="9">
+        <v>10</v>
+      </c>
+      <c r="O64" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="P64" s="19" t="s">
+        <v>408</v>
+      </c>
+      <c r="Q64" s="19">
+        <f t="shared" si="5"/>
+        <v>24.563</v>
+      </c>
+      <c r="R64" s="12"/>
+    </row>
+    <row r="65" ht="24" spans="1:18">
+      <c r="A65" s="2"/>
+      <c r="B65" s="7">
+        <f>ROW(B65)-ROW($B$2)</f>
+        <v>63</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="I65" s="9"/>
+      <c r="J65" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="K65" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="L65" s="9">
+        <v>1</v>
+      </c>
+      <c r="M65" s="9">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="N65" s="9">
+        <v>10</v>
+      </c>
+      <c r="O65" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="P65" s="17" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q65" s="17">
+        <f t="shared" si="5"/>
+        <v>14.773</v>
+      </c>
+      <c r="R65" s="9"/>
+    </row>
+    <row r="66" ht="36" spans="1:18">
+      <c r="A66" s="2"/>
+      <c r="B66" s="10">
+        <f>ROW(B66)-ROW($B$2)</f>
+        <v>64</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="E66" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="F66" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="G66" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="H66" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="I66" s="12"/>
+      <c r="J66" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="K66" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="L66" s="12">
+        <v>1</v>
+      </c>
+      <c r="M66" s="9">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="N66" s="9">
+        <v>10</v>
+      </c>
+      <c r="O66" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="P66" s="19" t="s">
+        <v>424</v>
+      </c>
+      <c r="Q66" s="19">
+        <f t="shared" si="5"/>
+        <v>0.814</v>
+      </c>
+      <c r="R66" s="12"/>
+    </row>
+    <row r="67" ht="75.75" spans="1:18">
+      <c r="A67" s="2"/>
+      <c r="B67" s="10">
+        <f>ROW(B67)-ROW($B$2)</f>
+        <v>65</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E67" s="23" t="s">
+        <v>426</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="I67" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="J67" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="K67" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="L67" s="12">
+        <v>1</v>
+      </c>
+      <c r="M67" s="9">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="N67" s="9">
+        <v>10</v>
+      </c>
+      <c r="O67" s="28" t="s">
+        <v>428</v>
+      </c>
+      <c r="P67" s="19">
+        <v>15.26</v>
+      </c>
+      <c r="Q67" s="19">
+        <f t="shared" si="5"/>
+        <v>152.6</v>
+      </c>
+      <c r="R67" s="12"/>
+    </row>
+    <row r="68" ht="19.5" spans="1:17">
+      <c r="A68" s="2"/>
+      <c r="B68"/>
+      <c r="C68"/>
+      <c r="N68" s="29" t="s">
+        <v>429</v>
+      </c>
+      <c r="O68" s="30"/>
+      <c r="P68" s="30"/>
+      <c r="Q68" s="31">
+        <f>SUM(Q3:Q67)</f>
+        <v>349.4378</v>
+      </c>
+    </row>
+    <row r="69" ht="19.5" spans="1:17">
+      <c r="A69" s="2"/>
+      <c r="B69"/>
+      <c r="C69"/>
+      <c r="N69" s="29" t="s">
+        <v>430</v>
+      </c>
+      <c r="O69" s="30"/>
+      <c r="P69" s="30"/>
+      <c r="Q69" s="32">
+        <f>Q68/10</f>
+        <v>34.94378</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="K1:R1"/>
+    <mergeCell ref="N68:P68"/>
+    <mergeCell ref="N69:P69"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="O4" r:id="rId1" display="LCSC"/>
+    <hyperlink ref="O5" r:id="rId2" display="LCSC"/>
+    <hyperlink ref="O7" r:id="rId3" display="LCSC"/>
+    <hyperlink ref="O9" r:id="rId4" display="LCSC"/>
+    <hyperlink ref="O10" r:id="rId5" display="LCSC"/>
+    <hyperlink ref="O11" r:id="rId6" display="LCSC"/>
+    <hyperlink ref="O12" r:id="rId7" display="LCSC"/>
+    <hyperlink ref="O13" r:id="rId8" display="LCSC"/>
+    <hyperlink ref="O14" r:id="rId9" display="LCSC"/>
+    <hyperlink ref="O15" r:id="rId10" display="LCSC"/>
+    <hyperlink ref="O16" r:id="rId11" display="LCSC"/>
+    <hyperlink ref="O17" r:id="rId12" display="LCSC"/>
+    <hyperlink ref="O18" r:id="rId13" display="LCSC"/>
+    <hyperlink ref="O19" r:id="rId14" display="LCSC"/>
+    <hyperlink ref="O20" r:id="rId15" display="LCSC"/>
+    <hyperlink ref="O21" r:id="rId16" display="LCSC"/>
+    <hyperlink ref="O22" r:id="rId17" display="LCSC"/>
+    <hyperlink ref="O23" r:id="rId18" display="LCSC"/>
+    <hyperlink ref="O24" r:id="rId19" display="LCSC"/>
+    <hyperlink ref="O3" r:id="rId20" display="LCSC"/>
+    <hyperlink ref="O6" r:id="rId21" display="LCSC"/>
+    <hyperlink ref="O8" r:id="rId22" display="Digikey"/>
+    <hyperlink ref="O25" r:id="rId23" display="LCSC"/>
+    <hyperlink ref="O26" r:id="rId24" display="LCSC"/>
+    <hyperlink ref="O27" r:id="rId25" display="LCSC"/>
+    <hyperlink ref="O28" r:id="rId26" display="Digikey"/>
+    <hyperlink ref="O29" r:id="rId27" display="LCSC"/>
+    <hyperlink ref="O30" r:id="rId28" display="LCSC"/>
+    <hyperlink ref="O32" r:id="rId29" display="LCSC"/>
+    <hyperlink ref="O67" r:id="rId30" display="Order LCD Without touch panel"/>
+    <hyperlink ref="O66" r:id="rId31" display="LCSC"/>
+    <hyperlink ref="O65" r:id="rId32" display="LCSC"/>
+    <hyperlink ref="O64" r:id="rId33" display="LCSC"/>
+    <hyperlink ref="O63" r:id="rId34" display="LCSC"/>
+    <hyperlink ref="O62" r:id="rId35" display="LCSC"/>
+    <hyperlink ref="O61" r:id="rId36" display="LCSC"/>
+    <hyperlink ref="O60" r:id="rId37" display="LCSC"/>
+    <hyperlink ref="O59" r:id="rId38" display="LCSC"/>
+    <hyperlink ref="O58" r:id="rId39" display="LCSC"/>
+    <hyperlink ref="O57" r:id="rId40" display="LCSC"/>
+    <hyperlink ref="O56" r:id="rId41" display="LCSC"/>
+    <hyperlink ref="O55" r:id="rId42" display="-"/>
+    <hyperlink ref="O54" r:id="rId43" display="LCSC"/>
+    <hyperlink ref="O53" r:id="rId42" display="LCSC"/>
+    <hyperlink ref="O52" r:id="rId44" display="LCSC"/>
+    <hyperlink ref="O51" r:id="rId45" display="LCSC"/>
+    <hyperlink ref="O50" r:id="rId46" display="LCSC"/>
+    <hyperlink ref="O49" r:id="rId47" display="LCSC"/>
+    <hyperlink ref="O48" r:id="rId48" display="LCSC"/>
+    <hyperlink ref="O47" r:id="rId49" display="LCSC"/>
+    <hyperlink ref="O46" r:id="rId50" display="LCSC"/>
+    <hyperlink ref="O45" r:id="rId51" display="LCSC"/>
+    <hyperlink ref="O44" r:id="rId52" display="LCSC"/>
+    <hyperlink ref="O43" r:id="rId53" display="LCSC"/>
+    <hyperlink ref="O42" r:id="rId54" display="LCSC"/>
+    <hyperlink ref="O41" r:id="rId55" display="LCSC"/>
+    <hyperlink ref="O40" r:id="rId56" display="LCSC"/>
+    <hyperlink ref="O39" r:id="rId57" display="LCSC"/>
+    <hyperlink ref="O38" r:id="rId55" display="LCSC"/>
+    <hyperlink ref="O37" r:id="rId58" display="LCSC"/>
+    <hyperlink ref="O36" r:id="rId46" display="LCSC"/>
+    <hyperlink ref="O35" r:id="rId59" display="LCSC"/>
+    <hyperlink ref="O34" r:id="rId60" display="LCSC"/>
+    <hyperlink ref="O33" r:id="rId61" display="LCSC"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:R69"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="3.57142857142857" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="26.1428571428571" customWidth="1"/>
     <col min="5" max="5" width="29.5714285714286" customWidth="1"/>
@@ -6341,19 +10029,19 @@
         <v>10</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="O2" s="5" t="s">
         <v>13</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="R2" s="5" t="s">
         <v>16</v>
@@ -7154,7 +10842,7 @@
       </c>
       <c r="R17" s="9"/>
     </row>
-    <row r="18" s="1" customFormat="1" ht="36" spans="1:18">
+    <row r="18" s="1" customFormat="1" ht="24" spans="1:18">
       <c r="A18" s="6"/>
       <c r="B18" s="10">
         <f>ROW(B18)-ROW($B$2)</f>
@@ -7207,7 +10895,7 @@
       </c>
       <c r="R18" s="12"/>
     </row>
-    <row r="19" s="1" customFormat="1" ht="24" spans="1:18">
+    <row r="19" s="1" customFormat="1" spans="1:18">
       <c r="A19" s="6"/>
       <c r="B19" s="7">
         <f>ROW(B19)-ROW($B$2)</f>
@@ -7260,7 +10948,7 @@
       </c>
       <c r="R19" s="9"/>
     </row>
-    <row r="20" s="1" customFormat="1" ht="24" spans="1:18">
+    <row r="20" s="1" customFormat="1" spans="1:18">
       <c r="A20" s="6"/>
       <c r="B20" s="10">
         <f>ROW(B20)-ROW($B$2)</f>
@@ -7313,7 +11001,7 @@
       </c>
       <c r="R20" s="12"/>
     </row>
-    <row r="21" s="1" customFormat="1" ht="36" spans="1:18">
+    <row r="21" s="1" customFormat="1" ht="25.5" spans="1:18">
       <c r="A21" s="6"/>
       <c r="B21" s="7">
         <f>ROW(B21)-ROW($B$2)</f>
@@ -7488,7 +11176,7 @@
         <v>164</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>166</v>
@@ -7541,7 +11229,7 @@
         <v>172</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>174</v>
@@ -7578,7 +11266,7 @@
       </c>
       <c r="R25" s="9"/>
     </row>
-    <row r="26" s="1" customFormat="1" ht="72" spans="1:18">
+    <row r="26" s="1" customFormat="1" ht="60" spans="1:18">
       <c r="A26" s="6"/>
       <c r="B26" s="10">
         <f>ROW(B26)-ROW($B$2)</f>
@@ -7594,7 +11282,7 @@
         <v>179</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="G26" s="12" t="s">
         <v>180</v>
@@ -7647,7 +11335,7 @@
         <v>185</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>186</v>
@@ -7684,7 +11372,7 @@
       </c>
       <c r="R27" s="9"/>
     </row>
-    <row r="28" s="1" customFormat="1" ht="24" spans="1:18">
+    <row r="28" s="1" customFormat="1" spans="1:18">
       <c r="A28" s="6"/>
       <c r="B28" s="10">
         <f>ROW(B28)-ROW($B$2)</f>
@@ -7700,7 +11388,7 @@
         <v>191</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="G28" s="12" t="s">
         <v>192</v>
@@ -7753,7 +11441,7 @@
         <v>197</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="G29" s="9" t="s">
         <v>199</v>
@@ -7790,7 +11478,7 @@
       </c>
       <c r="R29" s="9"/>
     </row>
-    <row r="30" s="1" customFormat="1" ht="36" spans="1:18">
+    <row r="30" s="1" customFormat="1" ht="24" spans="1:18">
       <c r="A30" s="6"/>
       <c r="B30" s="10">
         <f>ROW(B30)-ROW($B$2)</f>
@@ -7806,7 +11494,7 @@
         <v>205</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>207</v>
@@ -7859,7 +11547,7 @@
         <v>213</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>214</v>
@@ -8270,7 +11958,7 @@
       </c>
       <c r="R38" s="12"/>
     </row>
-    <row r="39" s="1" customFormat="1" ht="24" spans="1:18">
+    <row r="39" s="1" customFormat="1" spans="1:18">
       <c r="A39" s="6"/>
       <c r="B39" s="7">
         <f>ROW(B39)-ROW($B$2)</f>
@@ -8323,7 +12011,7 @@
       </c>
       <c r="R39" s="9"/>
     </row>
-    <row r="40" s="1" customFormat="1" ht="48" spans="1:18">
+    <row r="40" s="1" customFormat="1" ht="36" spans="1:18">
       <c r="A40" s="6"/>
       <c r="B40" s="10">
         <f>ROW(B40)-ROW($B$2)</f>
@@ -8695,7 +12383,7 @@
       </c>
       <c r="R46" s="12"/>
     </row>
-    <row r="47" s="1" customFormat="1" ht="24" spans="1:18">
+    <row r="47" s="1" customFormat="1" spans="1:18">
       <c r="A47" s="6"/>
       <c r="B47" s="7">
         <f>ROW(B47)-ROW($B$2)</f>
@@ -8907,7 +12595,7 @@
       </c>
       <c r="R50" s="12"/>
     </row>
-    <row r="51" s="1" customFormat="1" ht="24" spans="1:18">
+    <row r="51" s="1" customFormat="1" spans="1:18">
       <c r="A51" s="6"/>
       <c r="B51" s="7">
         <f>ROW(B51)-ROW($B$2)</f>
@@ -9173,7 +12861,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="56" s="1" customFormat="1" ht="24" spans="1:18">
+    <row r="56" s="1" customFormat="1" spans="1:18">
       <c r="A56" s="6"/>
       <c r="B56" s="10">
         <f>ROW(B56)-ROW($B$2)</f>
@@ -9189,7 +12877,7 @@
         <v>344</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="G56" s="12" t="s">
         <v>345</v>
@@ -9221,12 +12909,12 @@
         <v>0.1012</v>
       </c>
       <c r="Q56" s="19">
-        <f t="shared" ref="Q56:Q66" si="5">P56*N56</f>
+        <f t="shared" ref="Q56:Q67" si="5">P56*N56</f>
         <v>20.24</v>
       </c>
       <c r="R56" s="12"/>
     </row>
-    <row r="57" s="1" customFormat="1" ht="24" spans="1:18">
+    <row r="57" s="1" customFormat="1" spans="1:18">
       <c r="A57" s="6"/>
       <c r="B57" s="7">
         <f>ROW(B57)-ROW($B$2)</f>
@@ -9242,7 +12930,7 @@
         <v>351</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="G57" s="9" t="s">
         <v>352</v>
@@ -9279,7 +12967,7 @@
       </c>
       <c r="R57" s="9"/>
     </row>
-    <row r="58" s="1" customFormat="1" ht="24" spans="1:18">
+    <row r="58" s="1" customFormat="1" spans="1:18">
       <c r="A58" s="6"/>
       <c r="B58" s="10">
         <f>ROW(B58)-ROW($B$2)</f>
@@ -9295,7 +12983,7 @@
         <v>344</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="G58" s="12" t="s">
         <v>359</v>
@@ -9401,7 +13089,7 @@
         <v>374</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="G60" s="12" t="s">
         <v>375</v>
@@ -9650,7 +13338,7 @@
       </c>
       <c r="R64" s="12"/>
     </row>
-    <row r="65" s="1" customFormat="1" ht="24" spans="1:18">
+    <row r="65" s="1" customFormat="1" spans="1:18">
       <c r="A65" s="6"/>
       <c r="B65" s="7">
         <f>ROW(B65)-ROW($B$2)</f>
@@ -9806,15 +13494,13 @@
         <v>15.26</v>
       </c>
       <c r="Q67" s="19">
-        <f>P67*N67</f>
+        <f t="shared" si="5"/>
         <v>1526</v>
       </c>
       <c r="R67" s="12"/>
     </row>
     <row r="68" ht="19.5" spans="1:17">
       <c r="A68" s="2"/>
-      <c r="B68"/>
-      <c r="C68"/>
       <c r="N68" s="29" t="s">
         <v>429</v>
       </c>
@@ -9827,8 +13513,6 @@
     </row>
     <row r="69" ht="19.5" spans="1:17">
       <c r="A69" s="2"/>
-      <c r="B69"/>
-      <c r="C69"/>
       <c r="N69" s="29" t="s">
         <v>430</v>
       </c>
